--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260616.xlsx
@@ -689,17 +689,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>74,678,927</t>
+          <t>34,273,242</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>34,273,242</t>
+          <t>74,678,927</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>246,789,781</t>
+          <t>117,904,111</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>117,904,111</t>
+          <t>246,789,781</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>37,443,989</t>
+          <t>144,264,306</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>144,264,306</t>
+          <t>37,443,989</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>10,623,248</t>
+          <t>13,674,274</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>13,674,274</t>
+          <t>10,623,248</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
